--- a/output/topology_excel/13079.xlsx
+++ b/output/topology_excel/13079.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>275409</v>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>19204</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>275409</v>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>38</v>
-      </c>
-      <c r="J3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>275409</v>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>3680</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>40</v>
-      </c>
-      <c r="J4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>275409</v>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>197</v>
       </c>
       <c r="F5" t="n">
-        <v>19204</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>197</v>
-      </c>
-      <c r="J5" t="n">
         <v>104</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>275409</v>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>126</v>
       </c>
       <c r="F6" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>126</v>
-      </c>
-      <c r="J6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>275409</v>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>3680</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>63</v>
-      </c>
-      <c r="J7" t="n">
         <v>21</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>19204</v>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>80</v>
-      </c>
-      <c r="J8" t="n">
         <v>8</v>
       </c>
     </row>

--- a/output/topology_excel/13079.xlsx
+++ b/output/topology_excel/13079.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,15 +564,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
@@ -586,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -608,10 +608,142 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
+        <v>114</v>
+      </c>
+      <c r="F8" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>80</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>126</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>135</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>198</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>163</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/13079.xlsx
+++ b/output/topology_excel/13079.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,162 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Width_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Length_7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Width_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Length_8</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Width_8</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Length_9</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Width_9</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Length_10</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Width_10</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Length_11</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Width_11</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Length_12</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Width_12</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Length_13</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Width_13</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Length_14</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Width_14</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Length_15</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Width_15</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Length_16</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Width_16</t>
         </is>
       </c>
     </row>
@@ -481,6 +631,36 @@
       <c r="F2" t="n">
         <v>21</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +683,36 @@
       <c r="F3" t="n">
         <v>7</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +735,36 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +787,36 @@
       <c r="F5" t="n">
         <v>7</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -561,13 +831,103 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -583,14 +943,48 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -611,8 +1005,38 @@
         <v>114</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +1059,36 @@
       <c r="F9" t="n">
         <v>8</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +1111,36 @@
       <c r="F10" t="n">
         <v>7</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -671,7 +1155,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>135</v>
@@ -679,10 +1163,44 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
+      <c r="G11" t="n">
+        <v>198</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
@@ -696,18 +1214,48 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>198</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,33 +1266,41 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>163</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
